--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>rover_diag_manager provides the platform's computer-health monitor (rover_diag_manager_node: CPU usage, CPU temperature, RAM and root-disk usage, published as rover_msgs/SystemStatus and as an 'OS status' diagnostic) and the configuration/launch of the diagnostic_aggregator node that groups every rover node's /diagnostics statuses into the diagnostics_agg tree shown by the Cockpit diagnostics page. It does not itself produce the drive, battery, E-stop or sensor diagnostics; those come from the owning packages and are only grouped here.</t>
+          <t>rover_diag_manager provides the platform's computer-health monitor (rover_diag_manager_node: CPU usage, CPU temperature, RAM and root-disk usage, published as rover_msgs/SystemStatus and as an 'OS status' diagnostic) and the configuration/launch of the diagnostic_aggregator node that groups every rover node's /diagnostics statuses into the diagnostics_agg tree shown by the drive UI diagnostics page. It does not itself produce the drive, battery, E-stop or sensor diagnostics; those come from the owning packages and are only grouped here.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
@@ -1078,7 +1078,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>The rover_diag_manager shall launch a diagnostic_aggregator aggregator_node named rover_diagnostic_aggregator that subscribes to the namespaced diagnostics topic and publishes diagnostics_agg and diagnostics_toplevel_state inside the launch namespace (ROVER_NAMESPACE).</t>
+          <t>The rover_diag_manager shall launch a diagnostic_aggregator aggregator_node named rover_diagnostic_aggregator that subscribes to the namespaced diagnostics topic and publishes diagnostics_agg and diagnostics_toplevel_state inside the launch namespace (ROVER_SYSTEM_NAMESPACE).</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>The rover_diag_manager launch file shall accept the arguments log_level (DEBUG/INFO/WARN/ERROR/FATAL, default INFO), namespace (default $ROVER_NAMESPACE or empty), system_diag_config_path (default config/system_diag.yaml) and diagnostic_aggregator_config_path (default config/diagnostic_aggregator.yaml).</t>
+          <t>The rover_diag_manager launch file shall accept the arguments log_level (DEBUG/INFO/WARN/ERROR/FATAL, default INFO), namespace (default $ROVER_SYSTEM_NAMESPACE or empty), system_diag_config_path (default config/system_diag.yaml) and diagnostic_aggregator_config_path (default config/diagnostic_aggregator.yaml).</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DIAG_MANAGER-SWRS-V-001.xlsx
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The rover_diag_manager shall group diagnostic statuses by node-name prefix into the aggregator paths Computer (rover_diag_manager_node), Drive (rover_hardware_controller, controller_manager), Battery (rover_battery_node), Localization (rover_ekf_node, rover_ekf_global_node, rover_navsat_transform_node), GPS (rover_gps_node, rover_gps_heading_node), Lidar (rover_rs16_lidar_node), Lighting (rover_led_driver, rover_led_controller), Teleop (rover_crsf_teleop_node), Motion (rover_motion_lock_node, rover_twist_mux_node) and Safety (rover_safety_node, rover_led_safety_node).</t>
+          <t>The rover_diag_manager shall group diagnostic statuses by node-name prefix into the aggregator paths Computer (rover_diag_manager_node), Drive (rover_hardware_controller, controller_manager), Battery (rover_battery_node), Localization (rover_ekf_node, rover_ekf_global_node, rover_navsat_transform_node), GPS (rover_gps_node, rover_gps_heading_node; only with ROVER_SYSTEM_USE_GPS), Lidar (rover_rs16_lidar_node; only with ROVER_SYSTEM_USE_LIDAR), Lighting (rover_led_driver, rover_led_controller), Teleop (rover_crsf_teleop_node), Motion (rover_motion_lock_node, rover_twist_mux_node) and Safety (rover_safety_node, rover_led_safety_node).</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
